--- a/BWI/bestwine_output/bestwine_Singapore.xlsx
+++ b/BWI/bestwine_output/bestwine_Singapore.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA362"/>
+  <dimension ref="A1:AA364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -39567,6 +39567,188 @@
         </is>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>Mr Vino Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>Mr Vino</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>167420</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr"/>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>629 Aljunied Road</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="inlineStr">
+        <is>
+          <t>389838</t>
+        </is>
+      </c>
+      <c r="I363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mrvino.sg</t>
+        </is>
+      </c>
+      <c r="J363" s="2" t="inlineStr"/>
+      <c r="K363" s="2" t="inlineStr"/>
+      <c r="L363" s="2" t="inlineStr"/>
+      <c r="M363" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N363" s="2" t="inlineStr">
+        <is>
+          <t>hello@mrvino.sg</t>
+        </is>
+      </c>
+      <c r="O363" s="2" t="inlineStr"/>
+      <c r="P363" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q363" s="2" t="inlineStr"/>
+      <c r="R363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vino-pazzo</t>
+        </is>
+      </c>
+      <c r="S363" s="2" t="inlineStr">
+        <is>
+          <t>http://www.facebook.com/mrvinosg</t>
+        </is>
+      </c>
+      <c r="T363" s="2" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/mrvinosg</t>
+        </is>
+      </c>
+      <c r="U363" s="2" t="inlineStr">
+        <is>
+          <t>http://www.twitter.com/mrvinosg</t>
+        </is>
+      </c>
+      <c r="V363" s="2" t="inlineStr"/>
+      <c r="W363" s="2" t="inlineStr">
+        <is>
+          <t>Claudio Nuti</t>
+        </is>
+      </c>
+      <c r="X363" s="2" t="inlineStr">
+        <is>
+          <t>Founder, Director</t>
+        </is>
+      </c>
+      <c r="Y363" s="2" t="inlineStr"/>
+      <c r="Z363" s="2" t="inlineStr"/>
+      <c r="AA363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/claudio-nuti-514391103/</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>Tasteturkey Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>Tasteturkey Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>51438</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Square, 60 Paya Lebar Road, Geylang</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>409051</t>
+        </is>
+      </c>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tasteturkey.sg</t>
+        </is>
+      </c>
+      <c r="J364" s="2" t="inlineStr"/>
+      <c r="K364" s="2" t="inlineStr"/>
+      <c r="L364" s="2" t="inlineStr"/>
+      <c r="M364" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N364" s="2" t="inlineStr">
+        <is>
+          <t>emre.goroglu@tasteturkey.sg</t>
+        </is>
+      </c>
+      <c r="O364" s="2" t="inlineStr"/>
+      <c r="P364" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q364" s="2" t="inlineStr"/>
+      <c r="R364" s="2" t="inlineStr">
+        <is>
+          <t>http://linkedin.com/company/tasteturkeysingapore/</t>
+        </is>
+      </c>
+      <c r="S364" s="2" t="inlineStr"/>
+      <c r="T364" s="2" t="inlineStr"/>
+      <c r="U364" s="2" t="inlineStr"/>
+      <c r="V364" s="2" t="inlineStr"/>
+      <c r="W364" s="2" t="inlineStr"/>
+      <c r="X364" s="2" t="inlineStr"/>
+      <c r="Y364" s="2" t="inlineStr"/>
+      <c r="Z364" s="2" t="inlineStr"/>
+      <c r="AA364" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Singapore.xlsx
+++ b/BWI/bestwine_output/bestwine_Singapore.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA364"/>
+  <dimension ref="A1:AA366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -39749,6 +39749,180 @@
       <c r="Z364" s="2" t="inlineStr"/>
       <c r="AA364" s="2" t="inlineStr"/>
     </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>The First Pour Pte Ltd</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>The First Pour Pte Ltd</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>119458</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>Henderson Industrial Park, 215 Henderson Road, Bukit Merah</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>159554</t>
+        </is>
+      </c>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>https://thefirstpour.com</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="inlineStr"/>
+      <c r="K365" s="2" t="inlineStr"/>
+      <c r="L365" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M365" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N365" s="2" t="inlineStr">
+        <is>
+          <t>sales@thefirstpour.com</t>
+        </is>
+      </c>
+      <c r="O365" s="2" t="inlineStr">
+        <is>
+          <t>+65 6733 7663</t>
+        </is>
+      </c>
+      <c r="P365" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q365" s="2" t="inlineStr">
+        <is>
+          <t>202011397W</t>
+        </is>
+      </c>
+      <c r="R365" s="2" t="inlineStr"/>
+      <c r="S365" s="2" t="inlineStr"/>
+      <c r="T365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thefirstpour/</t>
+        </is>
+      </c>
+      <c r="U365" s="2" t="inlineStr"/>
+      <c r="V365" s="2" t="inlineStr"/>
+      <c r="W365" s="2" t="inlineStr"/>
+      <c r="X365" s="2" t="inlineStr"/>
+      <c r="Y365" s="2" t="inlineStr"/>
+      <c r="Z365" s="2" t="inlineStr"/>
+      <c r="AA365" s="2" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>Tasteturkey Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>Tasteturkey Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>51438</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Square, 60 Paya Lebar Road, Geylang</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>409051</t>
+        </is>
+      </c>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tasteturkey.sg</t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="inlineStr"/>
+      <c r="K366" s="2" t="inlineStr"/>
+      <c r="L366" s="2" t="inlineStr"/>
+      <c r="M366" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N366" s="2" t="inlineStr">
+        <is>
+          <t>emre.goroglu@tasteturkey.sg</t>
+        </is>
+      </c>
+      <c r="O366" s="2" t="inlineStr"/>
+      <c r="P366" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q366" s="2" t="inlineStr"/>
+      <c r="R366" s="2" t="inlineStr">
+        <is>
+          <t>http://linkedin.com/company/tasteturkeysingapore/</t>
+        </is>
+      </c>
+      <c r="S366" s="2" t="inlineStr"/>
+      <c r="T366" s="2" t="inlineStr"/>
+      <c r="U366" s="2" t="inlineStr"/>
+      <c r="V366" s="2" t="inlineStr"/>
+      <c r="W366" s="2" t="inlineStr"/>
+      <c r="X366" s="2" t="inlineStr"/>
+      <c r="Y366" s="2" t="inlineStr"/>
+      <c r="Z366" s="2" t="inlineStr"/>
+      <c r="AA366" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Singapore.xlsx
+++ b/BWI/bestwine_output/bestwine_Singapore.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA366"/>
+  <dimension ref="A1:AA370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -39923,6 +39923,414 @@
       <c r="Z366" s="2" t="inlineStr"/>
       <c r="AA366" s="2" t="inlineStr"/>
     </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>Cold Storage Supermarket</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>Cold Storage Supermarket</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>11868</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>21 Tampines North Drive 2, #03-01</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>528765</t>
+        </is>
+      </c>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>https://coldstorage.com.sg</t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="inlineStr"/>
+      <c r="K367" s="2" t="inlineStr"/>
+      <c r="L367" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M367" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N367" s="2" t="inlineStr">
+        <is>
+          <t>csonline@coldstorage.com.sg</t>
+        </is>
+      </c>
+      <c r="O367" s="2" t="inlineStr">
+        <is>
+          <t>+65 1800 891 8100</t>
+        </is>
+      </c>
+      <c r="P367" s="2" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="Q367" s="2" t="inlineStr">
+        <is>
+          <t>22661900A</t>
+        </is>
+      </c>
+      <c r="R367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cold-storage-singapore/</t>
+        </is>
+      </c>
+      <c r="S367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sg.coldstorage</t>
+        </is>
+      </c>
+      <c r="T367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coldstoragesg</t>
+        </is>
+      </c>
+      <c r="U367" s="2" t="inlineStr"/>
+      <c r="V367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCSjKnwdfRFumraG7tIp7Vpw</t>
+        </is>
+      </c>
+      <c r="W367" s="2" t="inlineStr">
+        <is>
+          <t>Elyse Jong</t>
+        </is>
+      </c>
+      <c r="X367" s="2" t="inlineStr">
+        <is>
+          <t>Buying Executive</t>
+        </is>
+      </c>
+      <c r="Y367" s="2" t="inlineStr"/>
+      <c r="Z367" s="2" t="inlineStr"/>
+      <c r="AA367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elyse-jong-37a03a13a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>Cold Storage Supermarket</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>Cold Storage Supermarket</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>11868</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>21 Tampines North Drive 2, #03-01</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>528765</t>
+        </is>
+      </c>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>https://coldstorage.com.sg</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="inlineStr"/>
+      <c r="K368" s="2" t="inlineStr"/>
+      <c r="L368" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M368" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N368" s="2" t="inlineStr">
+        <is>
+          <t>csonline@coldstorage.com.sg</t>
+        </is>
+      </c>
+      <c r="O368" s="2" t="inlineStr">
+        <is>
+          <t>+65 1800 891 8100</t>
+        </is>
+      </c>
+      <c r="P368" s="2" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="Q368" s="2" t="inlineStr">
+        <is>
+          <t>22661900A</t>
+        </is>
+      </c>
+      <c r="R368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cold-storage-singapore/</t>
+        </is>
+      </c>
+      <c r="S368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sg.coldstorage</t>
+        </is>
+      </c>
+      <c r="T368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coldstoragesg</t>
+        </is>
+      </c>
+      <c r="U368" s="2" t="inlineStr"/>
+      <c r="V368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCSjKnwdfRFumraG7tIp7Vpw</t>
+        </is>
+      </c>
+      <c r="W368" s="2" t="inlineStr">
+        <is>
+          <t>Lorenzo Claro</t>
+        </is>
+      </c>
+      <c r="X368" s="2" t="inlineStr">
+        <is>
+          <t>Store Manager</t>
+        </is>
+      </c>
+      <c r="Y368" s="2" t="inlineStr"/>
+      <c r="Z368" s="2" t="inlineStr"/>
+      <c r="AA368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lorenzo-claro-270657a6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>The First Pour Pte Ltd</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>The First Pour Pte Ltd</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>119458</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>Henderson Industrial Park, 215 Henderson Road, Bukit Merah</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>159554</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>https://thefirstpour.com</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="inlineStr"/>
+      <c r="K369" s="2" t="inlineStr"/>
+      <c r="L369" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M369" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N369" s="2" t="inlineStr">
+        <is>
+          <t>sales@thefirstpour.com</t>
+        </is>
+      </c>
+      <c r="O369" s="2" t="inlineStr">
+        <is>
+          <t>+65 6733 7663</t>
+        </is>
+      </c>
+      <c r="P369" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q369" s="2" t="inlineStr">
+        <is>
+          <t>202011397W</t>
+        </is>
+      </c>
+      <c r="R369" s="2" t="inlineStr"/>
+      <c r="S369" s="2" t="inlineStr"/>
+      <c r="T369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thefirstpour/</t>
+        </is>
+      </c>
+      <c r="U369" s="2" t="inlineStr"/>
+      <c r="V369" s="2" t="inlineStr"/>
+      <c r="W369" s="2" t="inlineStr"/>
+      <c r="X369" s="2" t="inlineStr"/>
+      <c r="Y369" s="2" t="inlineStr"/>
+      <c r="Z369" s="2" t="inlineStr"/>
+      <c r="AA369" s="2" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>Tasteturkey Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>Tasteturkey Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>51438</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Square, 60 Paya Lebar Road, Geylang</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>409051</t>
+        </is>
+      </c>
+      <c r="I370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tasteturkey.sg</t>
+        </is>
+      </c>
+      <c r="J370" s="2" t="inlineStr"/>
+      <c r="K370" s="2" t="inlineStr"/>
+      <c r="L370" s="2" t="inlineStr"/>
+      <c r="M370" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N370" s="2" t="inlineStr">
+        <is>
+          <t>emre.goroglu@tasteturkey.sg</t>
+        </is>
+      </c>
+      <c r="O370" s="2" t="inlineStr"/>
+      <c r="P370" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q370" s="2" t="inlineStr"/>
+      <c r="R370" s="2" t="inlineStr">
+        <is>
+          <t>http://linkedin.com/company/tasteturkeysingapore/</t>
+        </is>
+      </c>
+      <c r="S370" s="2" t="inlineStr"/>
+      <c r="T370" s="2" t="inlineStr"/>
+      <c r="U370" s="2" t="inlineStr"/>
+      <c r="V370" s="2" t="inlineStr"/>
+      <c r="W370" s="2" t="inlineStr"/>
+      <c r="X370" s="2" t="inlineStr"/>
+      <c r="Y370" s="2" t="inlineStr"/>
+      <c r="Z370" s="2" t="inlineStr"/>
+      <c r="AA370" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Singapore.xlsx
+++ b/BWI/bestwine_output/bestwine_Singapore.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA370"/>
+  <dimension ref="A1:AA378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -40331,6 +40331,818 @@
       <c r="Z370" s="2" t="inlineStr"/>
       <c r="AA370" s="2" t="inlineStr"/>
     </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>Little Farms Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>Little Farms</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>167636</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr"/>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>491 River Valley Rd</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>248371</t>
+        </is>
+      </c>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.littlefarms.com</t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="inlineStr"/>
+      <c r="K371" s="2" t="inlineStr"/>
+      <c r="L371" s="2" t="inlineStr"/>
+      <c r="M371" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N371" s="2" t="inlineStr">
+        <is>
+          <t>info@littlefarms.com</t>
+        </is>
+      </c>
+      <c r="O371" s="2" t="inlineStr">
+        <is>
+          <t>+65 6262 0619</t>
+        </is>
+      </c>
+      <c r="P371" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q371" s="2" t="inlineStr"/>
+      <c r="R371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/little-farms/</t>
+        </is>
+      </c>
+      <c r="S371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LittleFarmsGrocer/</t>
+        </is>
+      </c>
+      <c r="T371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/littlefarms/</t>
+        </is>
+      </c>
+      <c r="U371" s="2" t="inlineStr"/>
+      <c r="V371" s="2" t="inlineStr"/>
+      <c r="W371" s="2" t="inlineStr">
+        <is>
+          <t>Joe Stevens</t>
+        </is>
+      </c>
+      <c r="X371" s="2" t="inlineStr">
+        <is>
+          <t>Co-Chairman and Ceo</t>
+        </is>
+      </c>
+      <c r="Y371" s="2" t="inlineStr"/>
+      <c r="Z371" s="2" t="inlineStr"/>
+      <c r="AA371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joe-stevens-500184130/</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>Little Farms Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>Little Farms</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>167636</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr"/>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>491 River Valley Rd</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>248371</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.littlefarms.com</t>
+        </is>
+      </c>
+      <c r="J372" s="2" t="inlineStr"/>
+      <c r="K372" s="2" t="inlineStr"/>
+      <c r="L372" s="2" t="inlineStr"/>
+      <c r="M372" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N372" s="2" t="inlineStr">
+        <is>
+          <t>info@littlefarms.com</t>
+        </is>
+      </c>
+      <c r="O372" s="2" t="inlineStr">
+        <is>
+          <t>+65 6262 0619</t>
+        </is>
+      </c>
+      <c r="P372" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q372" s="2" t="inlineStr"/>
+      <c r="R372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/little-farms/</t>
+        </is>
+      </c>
+      <c r="S372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LittleFarmsGrocer/</t>
+        </is>
+      </c>
+      <c r="T372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/littlefarms/</t>
+        </is>
+      </c>
+      <c r="U372" s="2" t="inlineStr"/>
+      <c r="V372" s="2" t="inlineStr"/>
+      <c r="W372" s="2" t="inlineStr">
+        <is>
+          <t>Tom Gray</t>
+        </is>
+      </c>
+      <c r="X372" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y372" s="2" t="inlineStr"/>
+      <c r="Z372" s="2" t="inlineStr"/>
+      <c r="AA372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tom-gray-33a39727/</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>Little Farms Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>Little Farms</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>167636</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr"/>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>491 River Valley Rd</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>248371</t>
+        </is>
+      </c>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.littlefarms.com</t>
+        </is>
+      </c>
+      <c r="J373" s="2" t="inlineStr"/>
+      <c r="K373" s="2" t="inlineStr"/>
+      <c r="L373" s="2" t="inlineStr"/>
+      <c r="M373" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N373" s="2" t="inlineStr">
+        <is>
+          <t>info@littlefarms.com</t>
+        </is>
+      </c>
+      <c r="O373" s="2" t="inlineStr">
+        <is>
+          <t>+65 6262 0619</t>
+        </is>
+      </c>
+      <c r="P373" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q373" s="2" t="inlineStr"/>
+      <c r="R373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/little-farms/</t>
+        </is>
+      </c>
+      <c r="S373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LittleFarmsGrocer/</t>
+        </is>
+      </c>
+      <c r="T373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/littlefarms/</t>
+        </is>
+      </c>
+      <c r="U373" s="2" t="inlineStr"/>
+      <c r="V373" s="2" t="inlineStr"/>
+      <c r="W373" s="2" t="inlineStr">
+        <is>
+          <t>Jessica Yin</t>
+        </is>
+      </c>
+      <c r="X373" s="2" t="inlineStr">
+        <is>
+          <t>Head of Buying</t>
+        </is>
+      </c>
+      <c r="Y373" s="2" t="inlineStr"/>
+      <c r="Z373" s="2" t="inlineStr"/>
+      <c r="AA373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jessica-yin-109bb914a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>Little Farms Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>Little Farms</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>167636</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr"/>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>491 River Valley Rd</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>248371</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.littlefarms.com</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr"/>
+      <c r="K374" s="2" t="inlineStr"/>
+      <c r="L374" s="2" t="inlineStr"/>
+      <c r="M374" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N374" s="2" t="inlineStr">
+        <is>
+          <t>info@littlefarms.com</t>
+        </is>
+      </c>
+      <c r="O374" s="2" t="inlineStr">
+        <is>
+          <t>+65 6262 0619</t>
+        </is>
+      </c>
+      <c r="P374" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q374" s="2" t="inlineStr"/>
+      <c r="R374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/little-farms/</t>
+        </is>
+      </c>
+      <c r="S374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LittleFarmsGrocer/</t>
+        </is>
+      </c>
+      <c r="T374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/littlefarms/</t>
+        </is>
+      </c>
+      <c r="U374" s="2" t="inlineStr"/>
+      <c r="V374" s="2" t="inlineStr"/>
+      <c r="W374" s="2" t="inlineStr">
+        <is>
+          <t>Lucile De Graaf</t>
+        </is>
+      </c>
+      <c r="X374" s="2" t="inlineStr">
+        <is>
+          <t>Head of Wine and Alcoholic Beverage</t>
+        </is>
+      </c>
+      <c r="Y374" s="2" t="inlineStr"/>
+      <c r="Z374" s="2" t="inlineStr"/>
+      <c r="AA374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luciledegraaf/</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>Cold Storage Supermarket</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>Cold Storage Supermarket</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>11868</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>21 Tampines North Drive 2, #03-01</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>528765</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>https://coldstorage.com.sg</t>
+        </is>
+      </c>
+      <c r="J375" s="2" t="inlineStr"/>
+      <c r="K375" s="2" t="inlineStr"/>
+      <c r="L375" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M375" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N375" s="2" t="inlineStr">
+        <is>
+          <t>csonline@coldstorage.com.sg</t>
+        </is>
+      </c>
+      <c r="O375" s="2" t="inlineStr">
+        <is>
+          <t>+65 1800 891 8100</t>
+        </is>
+      </c>
+      <c r="P375" s="2" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="Q375" s="2" t="inlineStr">
+        <is>
+          <t>22661900A</t>
+        </is>
+      </c>
+      <c r="R375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cold-storage-singapore/</t>
+        </is>
+      </c>
+      <c r="S375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sg.coldstorage</t>
+        </is>
+      </c>
+      <c r="T375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coldstoragesg</t>
+        </is>
+      </c>
+      <c r="U375" s="2" t="inlineStr"/>
+      <c r="V375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCSjKnwdfRFumraG7tIp7Vpw</t>
+        </is>
+      </c>
+      <c r="W375" s="2" t="inlineStr">
+        <is>
+          <t>Elyse Jong</t>
+        </is>
+      </c>
+      <c r="X375" s="2" t="inlineStr">
+        <is>
+          <t>Buying Executive</t>
+        </is>
+      </c>
+      <c r="Y375" s="2" t="inlineStr"/>
+      <c r="Z375" s="2" t="inlineStr"/>
+      <c r="AA375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elyse-jong-37a03a13a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>Cold Storage Supermarket</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>Cold Storage Supermarket</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>11868</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>21 Tampines North Drive 2, #03-01</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>528765</t>
+        </is>
+      </c>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>https://coldstorage.com.sg</t>
+        </is>
+      </c>
+      <c r="J376" s="2" t="inlineStr"/>
+      <c r="K376" s="2" t="inlineStr"/>
+      <c r="L376" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M376" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N376" s="2" t="inlineStr">
+        <is>
+          <t>csonline@coldstorage.com.sg</t>
+        </is>
+      </c>
+      <c r="O376" s="2" t="inlineStr">
+        <is>
+          <t>+65 1800 891 8100</t>
+        </is>
+      </c>
+      <c r="P376" s="2" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="Q376" s="2" t="inlineStr">
+        <is>
+          <t>22661900A</t>
+        </is>
+      </c>
+      <c r="R376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cold-storage-singapore/</t>
+        </is>
+      </c>
+      <c r="S376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sg.coldstorage</t>
+        </is>
+      </c>
+      <c r="T376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coldstoragesg</t>
+        </is>
+      </c>
+      <c r="U376" s="2" t="inlineStr"/>
+      <c r="V376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCSjKnwdfRFumraG7tIp7Vpw</t>
+        </is>
+      </c>
+      <c r="W376" s="2" t="inlineStr">
+        <is>
+          <t>Lorenzo Claro</t>
+        </is>
+      </c>
+      <c r="X376" s="2" t="inlineStr">
+        <is>
+          <t>Store Manager</t>
+        </is>
+      </c>
+      <c r="Y376" s="2" t="inlineStr"/>
+      <c r="Z376" s="2" t="inlineStr"/>
+      <c r="AA376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lorenzo-claro-270657a6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>The First Pour Pte Ltd</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>The First Pour Pte Ltd</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>119458</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>Henderson Industrial Park, 215 Henderson Road, Bukit Merah</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>159554</t>
+        </is>
+      </c>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>https://thefirstpour.com</t>
+        </is>
+      </c>
+      <c r="J377" s="2" t="inlineStr"/>
+      <c r="K377" s="2" t="inlineStr"/>
+      <c r="L377" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M377" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N377" s="2" t="inlineStr">
+        <is>
+          <t>sales@thefirstpour.com</t>
+        </is>
+      </c>
+      <c r="O377" s="2" t="inlineStr">
+        <is>
+          <t>+65 6733 7663</t>
+        </is>
+      </c>
+      <c r="P377" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q377" s="2" t="inlineStr">
+        <is>
+          <t>202011397W</t>
+        </is>
+      </c>
+      <c r="R377" s="2" t="inlineStr"/>
+      <c r="S377" s="2" t="inlineStr"/>
+      <c r="T377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thefirstpour/</t>
+        </is>
+      </c>
+      <c r="U377" s="2" t="inlineStr"/>
+      <c r="V377" s="2" t="inlineStr"/>
+      <c r="W377" s="2" t="inlineStr"/>
+      <c r="X377" s="2" t="inlineStr"/>
+      <c r="Y377" s="2" t="inlineStr"/>
+      <c r="Z377" s="2" t="inlineStr"/>
+      <c r="AA377" s="2" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>Tasteturkey Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>Tasteturkey Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>51438</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Square, 60 Paya Lebar Road, Geylang</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>409051</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tasteturkey.sg</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr"/>
+      <c r="K378" s="2" t="inlineStr"/>
+      <c r="L378" s="2" t="inlineStr"/>
+      <c r="M378" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N378" s="2" t="inlineStr">
+        <is>
+          <t>emre.goroglu@tasteturkey.sg</t>
+        </is>
+      </c>
+      <c r="O378" s="2" t="inlineStr"/>
+      <c r="P378" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q378" s="2" t="inlineStr"/>
+      <c r="R378" s="2" t="inlineStr">
+        <is>
+          <t>http://linkedin.com/company/tasteturkeysingapore/</t>
+        </is>
+      </c>
+      <c r="S378" s="2" t="inlineStr"/>
+      <c r="T378" s="2" t="inlineStr"/>
+      <c r="U378" s="2" t="inlineStr"/>
+      <c r="V378" s="2" t="inlineStr"/>
+      <c r="W378" s="2" t="inlineStr"/>
+      <c r="X378" s="2" t="inlineStr"/>
+      <c r="Y378" s="2" t="inlineStr"/>
+      <c r="Z378" s="2" t="inlineStr"/>
+      <c r="AA378" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Singapore.xlsx
+++ b/BWI/bestwine_output/bestwine_Singapore.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA378"/>
+  <dimension ref="A1:AA380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -41143,6 +41143,216 @@
       <c r="Z378" s="2" t="inlineStr"/>
       <c r="AA378" s="2" t="inlineStr"/>
     </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>Boundby Pte Ltd</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>Boundby Pte Ltd</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>122015</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>120 Tembeling Road, Geylang</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>423619</t>
+        </is>
+      </c>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>https://boundbywine.com</t>
+        </is>
+      </c>
+      <c r="J379" s="2" t="inlineStr"/>
+      <c r="K379" s="2" t="inlineStr"/>
+      <c r="L379" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M379" s="2" t="inlineStr"/>
+      <c r="N379" s="2" t="inlineStr">
+        <is>
+          <t>contact@boundbywine.com</t>
+        </is>
+      </c>
+      <c r="O379" s="2" t="inlineStr"/>
+      <c r="P379" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q379" s="2" t="inlineStr">
+        <is>
+          <t>201924491C</t>
+        </is>
+      </c>
+      <c r="R379" s="2" t="inlineStr"/>
+      <c r="S379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/boundbywine/</t>
+        </is>
+      </c>
+      <c r="T379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boundbywine/</t>
+        </is>
+      </c>
+      <c r="U379" s="2" t="inlineStr"/>
+      <c r="V379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@boundbywine4076/</t>
+        </is>
+      </c>
+      <c r="W379" s="2" t="inlineStr">
+        <is>
+          <t>Germaine Wong</t>
+        </is>
+      </c>
+      <c r="X379" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y379" s="2" t="inlineStr"/>
+      <c r="Z379" s="2" t="inlineStr"/>
+      <c r="AA379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/germaine-wong-0a9451128/</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>Boundby Pte Ltd</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>Boundby Pte Ltd</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>122015</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>120 Tembeling Road, Geylang</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>423619</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>https://boundbywine.com</t>
+        </is>
+      </c>
+      <c r="J380" s="2" t="inlineStr"/>
+      <c r="K380" s="2" t="inlineStr"/>
+      <c r="L380" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M380" s="2" t="inlineStr"/>
+      <c r="N380" s="2" t="inlineStr">
+        <is>
+          <t>contact@boundbywine.com</t>
+        </is>
+      </c>
+      <c r="O380" s="2" t="inlineStr"/>
+      <c r="P380" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q380" s="2" t="inlineStr">
+        <is>
+          <t>201924491C</t>
+        </is>
+      </c>
+      <c r="R380" s="2" t="inlineStr"/>
+      <c r="S380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/boundbywine/</t>
+        </is>
+      </c>
+      <c r="T380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boundbywine/</t>
+        </is>
+      </c>
+      <c r="U380" s="2" t="inlineStr"/>
+      <c r="V380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@boundbywine4076/</t>
+        </is>
+      </c>
+      <c r="W380" s="2" t="inlineStr">
+        <is>
+          <t>Elliot Braet</t>
+        </is>
+      </c>
+      <c r="X380" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y380" s="2" t="inlineStr"/>
+      <c r="Z380" s="2" t="inlineStr"/>
+      <c r="AA380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/braetelliot/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Singapore.xlsx
+++ b/BWI/bestwine_output/bestwine_Singapore.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA380"/>
+  <dimension ref="A1:AA385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -41353,6 +41353,543 @@
         </is>
       </c>
     </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>Culina Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>Culina Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>11790</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>24 Senoko Way</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>758046</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>http://www.culina.com.sg, https://eshop.culina.com.sg, https://www.culina.com</t>
+        </is>
+      </c>
+      <c r="J381" s="2" t="inlineStr"/>
+      <c r="K381" s="2" t="inlineStr"/>
+      <c r="L381" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="M381" s="2" t="inlineStr"/>
+      <c r="N381" s="2" t="inlineStr">
+        <is>
+          <t>info@culina.com.sg</t>
+        </is>
+      </c>
+      <c r="O381" s="2" t="inlineStr">
+        <is>
+          <t>+65 6753 6966</t>
+        </is>
+      </c>
+      <c r="P381" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q381" s="2" t="inlineStr">
+        <is>
+          <t>199404977Z</t>
+        </is>
+      </c>
+      <c r="R381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/culina-pte-ltd</t>
+        </is>
+      </c>
+      <c r="S381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/culinacomodempsey/</t>
+        </is>
+      </c>
+      <c r="T381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/culinacomodempsey</t>
+        </is>
+      </c>
+      <c r="U381" s="2" t="inlineStr"/>
+      <c r="V381" s="2" t="inlineStr"/>
+      <c r="W381" s="2" t="inlineStr">
+        <is>
+          <t>Yeo Leelyne</t>
+        </is>
+      </c>
+      <c r="X381" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y381" s="2" t="inlineStr"/>
+      <c r="Z381" s="2" t="inlineStr"/>
+      <c r="AA381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yeo-leelyne-a548451a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>Culina Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>Culina Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>11790</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>24 Senoko Way</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>758046</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>http://www.culina.com.sg, https://eshop.culina.com.sg, https://www.culina.com</t>
+        </is>
+      </c>
+      <c r="J382" s="2" t="inlineStr"/>
+      <c r="K382" s="2" t="inlineStr"/>
+      <c r="L382" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="M382" s="2" t="inlineStr"/>
+      <c r="N382" s="2" t="inlineStr">
+        <is>
+          <t>info@culina.com.sg</t>
+        </is>
+      </c>
+      <c r="O382" s="2" t="inlineStr">
+        <is>
+          <t>+65 6753 6966</t>
+        </is>
+      </c>
+      <c r="P382" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q382" s="2" t="inlineStr">
+        <is>
+          <t>199404977Z</t>
+        </is>
+      </c>
+      <c r="R382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/culina-pte-ltd</t>
+        </is>
+      </c>
+      <c r="S382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/culinacomodempsey/</t>
+        </is>
+      </c>
+      <c r="T382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/culinacomodempsey</t>
+        </is>
+      </c>
+      <c r="U382" s="2" t="inlineStr"/>
+      <c r="V382" s="2" t="inlineStr"/>
+      <c r="W382" s="2" t="inlineStr">
+        <is>
+          <t>Ken Goh Kheng Swee</t>
+        </is>
+      </c>
+      <c r="X382" s="2" t="inlineStr">
+        <is>
+          <t>Wine Manager</t>
+        </is>
+      </c>
+      <c r="Y382" s="2" t="inlineStr"/>
+      <c r="Z382" s="2" t="inlineStr"/>
+      <c r="AA382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ken-goh-kheng-swee-bb1478ab/</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>Culina Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>Culina Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>11790</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>24 Senoko Way</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>758046</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>http://www.culina.com.sg, https://eshop.culina.com.sg, https://www.culina.com</t>
+        </is>
+      </c>
+      <c r="J383" s="2" t="inlineStr"/>
+      <c r="K383" s="2" t="inlineStr"/>
+      <c r="L383" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="M383" s="2" t="inlineStr"/>
+      <c r="N383" s="2" t="inlineStr">
+        <is>
+          <t>info@culina.com.sg</t>
+        </is>
+      </c>
+      <c r="O383" s="2" t="inlineStr">
+        <is>
+          <t>+65 6753 6966</t>
+        </is>
+      </c>
+      <c r="P383" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q383" s="2" t="inlineStr">
+        <is>
+          <t>199404977Z</t>
+        </is>
+      </c>
+      <c r="R383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/culina-pte-ltd</t>
+        </is>
+      </c>
+      <c r="S383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/culinacomodempsey/</t>
+        </is>
+      </c>
+      <c r="T383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/culinacomodempsey</t>
+        </is>
+      </c>
+      <c r="U383" s="2" t="inlineStr"/>
+      <c r="V383" s="2" t="inlineStr"/>
+      <c r="W383" s="2" t="inlineStr">
+        <is>
+          <t>Renee Ang</t>
+        </is>
+      </c>
+      <c r="X383" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y383" s="2" t="inlineStr"/>
+      <c r="Z383" s="2" t="inlineStr"/>
+      <c r="AA383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/renee-ang-460420112/</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>Boundby Pte Ltd</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>Boundby Pte Ltd</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>122015</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>120 Tembeling Road, Geylang</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>423619</t>
+        </is>
+      </c>
+      <c r="I384" s="2" t="inlineStr">
+        <is>
+          <t>https://boundbywine.com</t>
+        </is>
+      </c>
+      <c r="J384" s="2" t="inlineStr"/>
+      <c r="K384" s="2" t="inlineStr"/>
+      <c r="L384" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M384" s="2" t="inlineStr"/>
+      <c r="N384" s="2" t="inlineStr">
+        <is>
+          <t>contact@boundbywine.com</t>
+        </is>
+      </c>
+      <c r="O384" s="2" t="inlineStr"/>
+      <c r="P384" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q384" s="2" t="inlineStr">
+        <is>
+          <t>201924491C</t>
+        </is>
+      </c>
+      <c r="R384" s="2" t="inlineStr"/>
+      <c r="S384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/boundbywine/</t>
+        </is>
+      </c>
+      <c r="T384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boundbywine/</t>
+        </is>
+      </c>
+      <c r="U384" s="2" t="inlineStr"/>
+      <c r="V384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@boundbywine4076/</t>
+        </is>
+      </c>
+      <c r="W384" s="2" t="inlineStr">
+        <is>
+          <t>Germaine Wong</t>
+        </is>
+      </c>
+      <c r="X384" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y384" s="2" t="inlineStr"/>
+      <c r="Z384" s="2" t="inlineStr"/>
+      <c r="AA384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/germaine-wong-0a9451128/</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>Boundby Pte Ltd</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>Boundby Pte Ltd</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>122015</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>120 Tembeling Road, Geylang</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>423619</t>
+        </is>
+      </c>
+      <c r="I385" s="2" t="inlineStr">
+        <is>
+          <t>https://boundbywine.com</t>
+        </is>
+      </c>
+      <c r="J385" s="2" t="inlineStr"/>
+      <c r="K385" s="2" t="inlineStr"/>
+      <c r="L385" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M385" s="2" t="inlineStr"/>
+      <c r="N385" s="2" t="inlineStr">
+        <is>
+          <t>contact@boundbywine.com</t>
+        </is>
+      </c>
+      <c r="O385" s="2" t="inlineStr"/>
+      <c r="P385" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q385" s="2" t="inlineStr">
+        <is>
+          <t>201924491C</t>
+        </is>
+      </c>
+      <c r="R385" s="2" t="inlineStr"/>
+      <c r="S385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/boundbywine/</t>
+        </is>
+      </c>
+      <c r="T385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boundbywine/</t>
+        </is>
+      </c>
+      <c r="U385" s="2" t="inlineStr"/>
+      <c r="V385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@boundbywine4076/</t>
+        </is>
+      </c>
+      <c r="W385" s="2" t="inlineStr">
+        <is>
+          <t>Elliot Braet</t>
+        </is>
+      </c>
+      <c r="X385" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y385" s="2" t="inlineStr"/>
+      <c r="Z385" s="2" t="inlineStr"/>
+      <c r="AA385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/braetelliot/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Singapore.xlsx
+++ b/BWI/bestwine_output/bestwine_Singapore.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA385"/>
+  <dimension ref="A1:AA386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -41890,6 +41890,103 @@
         </is>
       </c>
     </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>Via Serica Pte Ltd</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>Via Serica Pte Ltd</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>122481</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>50 Tagore Lane, Ang Mo Kio</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="inlineStr">
+        <is>
+          <t>787494</t>
+        </is>
+      </c>
+      <c r="I386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.viaserica.com.sg</t>
+        </is>
+      </c>
+      <c r="J386" s="2" t="inlineStr"/>
+      <c r="K386" s="2" t="inlineStr"/>
+      <c r="L386" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M386" s="2" t="inlineStr"/>
+      <c r="N386" s="2" t="inlineStr">
+        <is>
+          <t>sales@viaserica.com.sg</t>
+        </is>
+      </c>
+      <c r="O386" s="2" t="inlineStr"/>
+      <c r="P386" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q386" s="2" t="inlineStr">
+        <is>
+          <t>201918284Z</t>
+        </is>
+      </c>
+      <c r="R386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/viaserica/</t>
+        </is>
+      </c>
+      <c r="S386" s="2" t="inlineStr"/>
+      <c r="T386" s="2" t="inlineStr"/>
+      <c r="U386" s="2" t="inlineStr"/>
+      <c r="V386" s="2" t="inlineStr"/>
+      <c r="W386" s="2" t="inlineStr">
+        <is>
+          <t>Dennis Breckenridge</t>
+        </is>
+      </c>
+      <c r="X386" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y386" s="2" t="inlineStr"/>
+      <c r="Z386" s="2" t="inlineStr"/>
+      <c r="AA386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dennis-breckenridge-4a964011/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Singapore.xlsx
+++ b/BWI/bestwine_output/bestwine_Singapore.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA386"/>
+  <dimension ref="A1:AA388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -41987,6 +41987,196 @@
         </is>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>Cities Trade Pte Ltd</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>Cities Trade Pte Ltd</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>122330</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>7 Mandai Link, Sungei Kadut</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>728653</t>
+        </is>
+      </c>
+      <c r="I387" s="2" t="inlineStr">
+        <is>
+          <t>https://ctcleantrading.com.sg</t>
+        </is>
+      </c>
+      <c r="J387" s="2" t="inlineStr"/>
+      <c r="K387" s="2" t="inlineStr"/>
+      <c r="L387" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M387" s="2" t="inlineStr"/>
+      <c r="N387" s="2" t="inlineStr">
+        <is>
+          <t>ct.enquiry@ctcleantrading.com.sg</t>
+        </is>
+      </c>
+      <c r="O387" s="2" t="inlineStr"/>
+      <c r="P387" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q387" s="2" t="inlineStr">
+        <is>
+          <t>202000944N</t>
+        </is>
+      </c>
+      <c r="R387" s="2" t="inlineStr"/>
+      <c r="S387" s="2" t="inlineStr"/>
+      <c r="T387" s="2" t="inlineStr"/>
+      <c r="U387" s="2" t="inlineStr"/>
+      <c r="V387" s="2" t="inlineStr"/>
+      <c r="W387" s="2" t="inlineStr">
+        <is>
+          <t>Chris Toh</t>
+        </is>
+      </c>
+      <c r="X387" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y387" s="2" t="inlineStr"/>
+      <c r="Z387" s="2" t="inlineStr"/>
+      <c r="AA387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chris-toh-04926795/</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>Winecircle Pte Ltd</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>Winecircle Pte Ltd</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>122335</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>100 Peck Seah Street, Outram</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="inlineStr">
+        <is>
+          <t>079333</t>
+        </is>
+      </c>
+      <c r="I388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winecircle.sg</t>
+        </is>
+      </c>
+      <c r="J388" s="2" t="inlineStr"/>
+      <c r="K388" s="2" t="inlineStr"/>
+      <c r="L388" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M388" s="2" t="inlineStr"/>
+      <c r="N388" s="2" t="inlineStr">
+        <is>
+          <t>Friends@winecircle.sg</t>
+        </is>
+      </c>
+      <c r="O388" s="2" t="inlineStr"/>
+      <c r="P388" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q388" s="2" t="inlineStr">
+        <is>
+          <t>201915292C</t>
+        </is>
+      </c>
+      <c r="R388" s="2" t="inlineStr"/>
+      <c r="S388" s="2" t="inlineStr"/>
+      <c r="T388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winecirclesg</t>
+        </is>
+      </c>
+      <c r="U388" s="2" t="inlineStr"/>
+      <c r="V388" s="2" t="inlineStr"/>
+      <c r="W388" s="2" t="inlineStr">
+        <is>
+          <t>Jean-marie Lagier</t>
+        </is>
+      </c>
+      <c r="X388" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y388" s="2" t="inlineStr"/>
+      <c r="Z388" s="2" t="inlineStr"/>
+      <c r="AA388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jean-marie-lagier-4046374/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Singapore.xlsx
+++ b/BWI/bestwine_output/bestwine_Singapore.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA388"/>
+  <dimension ref="A1:AA391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -42177,6 +42177,289 @@
         </is>
       </c>
     </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>Blackbird Group Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>Blackbird Group Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>122332</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>International Plaza, 10 Anson Road, Downtown Core</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="inlineStr">
+        <is>
+          <t>079903</t>
+        </is>
+      </c>
+      <c r="I389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.blackbirdgroup.com.sg</t>
+        </is>
+      </c>
+      <c r="J389" s="2" t="inlineStr"/>
+      <c r="K389" s="2" t="inlineStr"/>
+      <c r="L389" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M389" s="2" t="inlineStr"/>
+      <c r="N389" s="2" t="inlineStr">
+        <is>
+          <t>info@blackbirdgroup.com.sg</t>
+        </is>
+      </c>
+      <c r="O389" s="2" t="inlineStr"/>
+      <c r="P389" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q389" s="2" t="inlineStr">
+        <is>
+          <t>201830342D</t>
+        </is>
+      </c>
+      <c r="R389" s="2" t="inlineStr"/>
+      <c r="S389" s="2" t="inlineStr"/>
+      <c r="T389" s="2" t="inlineStr"/>
+      <c r="U389" s="2" t="inlineStr"/>
+      <c r="V389" s="2" t="inlineStr"/>
+      <c r="W389" s="2" t="inlineStr">
+        <is>
+          <t>Richard Golds</t>
+        </is>
+      </c>
+      <c r="X389" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y389" s="2" t="inlineStr"/>
+      <c r="Z389" s="2" t="inlineStr"/>
+      <c r="AA389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/richard-golds-67b662a</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>Cities Trade Pte Ltd</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>Cities Trade Pte Ltd</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>122330</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>7 Mandai Link, Sungei Kadut</t>
+        </is>
+      </c>
+      <c r="H390" s="2" t="inlineStr">
+        <is>
+          <t>728653</t>
+        </is>
+      </c>
+      <c r="I390" s="2" t="inlineStr">
+        <is>
+          <t>https://ctcleantrading.com.sg</t>
+        </is>
+      </c>
+      <c r="J390" s="2" t="inlineStr"/>
+      <c r="K390" s="2" t="inlineStr"/>
+      <c r="L390" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M390" s="2" t="inlineStr"/>
+      <c r="N390" s="2" t="inlineStr">
+        <is>
+          <t>ct.enquiry@ctcleantrading.com.sg</t>
+        </is>
+      </c>
+      <c r="O390" s="2" t="inlineStr"/>
+      <c r="P390" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q390" s="2" t="inlineStr">
+        <is>
+          <t>202000944N</t>
+        </is>
+      </c>
+      <c r="R390" s="2" t="inlineStr"/>
+      <c r="S390" s="2" t="inlineStr"/>
+      <c r="T390" s="2" t="inlineStr"/>
+      <c r="U390" s="2" t="inlineStr"/>
+      <c r="V390" s="2" t="inlineStr"/>
+      <c r="W390" s="2" t="inlineStr">
+        <is>
+          <t>Chris Toh</t>
+        </is>
+      </c>
+      <c r="X390" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y390" s="2" t="inlineStr"/>
+      <c r="Z390" s="2" t="inlineStr"/>
+      <c r="AA390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chris-toh-04926795/</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>Winecircle Pte Ltd</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>Winecircle Pte Ltd</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>122335</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>100 Peck Seah Street, Outram</t>
+        </is>
+      </c>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>079333</t>
+        </is>
+      </c>
+      <c r="I391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winecircle.sg</t>
+        </is>
+      </c>
+      <c r="J391" s="2" t="inlineStr"/>
+      <c r="K391" s="2" t="inlineStr"/>
+      <c r="L391" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M391" s="2" t="inlineStr"/>
+      <c r="N391" s="2" t="inlineStr">
+        <is>
+          <t>Friends@winecircle.sg</t>
+        </is>
+      </c>
+      <c r="O391" s="2" t="inlineStr"/>
+      <c r="P391" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q391" s="2" t="inlineStr">
+        <is>
+          <t>201915292C</t>
+        </is>
+      </c>
+      <c r="R391" s="2" t="inlineStr"/>
+      <c r="S391" s="2" t="inlineStr"/>
+      <c r="T391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winecirclesg</t>
+        </is>
+      </c>
+      <c r="U391" s="2" t="inlineStr"/>
+      <c r="V391" s="2" t="inlineStr"/>
+      <c r="W391" s="2" t="inlineStr">
+        <is>
+          <t>Jean-marie Lagier</t>
+        </is>
+      </c>
+      <c r="X391" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y391" s="2" t="inlineStr"/>
+      <c r="Z391" s="2" t="inlineStr"/>
+      <c r="AA391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jean-marie-lagier-4046374/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Singapore.xlsx
+++ b/BWI/bestwine_output/bestwine_Singapore.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA391"/>
+  <dimension ref="A1:AA394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -42460,6 +42460,289 @@
         </is>
       </c>
     </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>Blackbird Group Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>Blackbird Group Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>122332</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>International Plaza, 10 Anson Road, Downtown Core</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>079903</t>
+        </is>
+      </c>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.blackbirdgroup.com.sg</t>
+        </is>
+      </c>
+      <c r="J392" s="2" t="inlineStr"/>
+      <c r="K392" s="2" t="inlineStr"/>
+      <c r="L392" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M392" s="2" t="inlineStr"/>
+      <c r="N392" s="2" t="inlineStr">
+        <is>
+          <t>info@blackbirdgroup.com.sg</t>
+        </is>
+      </c>
+      <c r="O392" s="2" t="inlineStr"/>
+      <c r="P392" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q392" s="2" t="inlineStr">
+        <is>
+          <t>201830342D</t>
+        </is>
+      </c>
+      <c r="R392" s="2" t="inlineStr"/>
+      <c r="S392" s="2" t="inlineStr"/>
+      <c r="T392" s="2" t="inlineStr"/>
+      <c r="U392" s="2" t="inlineStr"/>
+      <c r="V392" s="2" t="inlineStr"/>
+      <c r="W392" s="2" t="inlineStr">
+        <is>
+          <t>Richard Golds</t>
+        </is>
+      </c>
+      <c r="X392" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y392" s="2" t="inlineStr"/>
+      <c r="Z392" s="2" t="inlineStr"/>
+      <c r="AA392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/richard-golds-67b662a</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>Cities Trade Pte Ltd</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>Cities Trade Pte Ltd</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>122330</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>7 Mandai Link, Sungei Kadut</t>
+        </is>
+      </c>
+      <c r="H393" s="2" t="inlineStr">
+        <is>
+          <t>728653</t>
+        </is>
+      </c>
+      <c r="I393" s="2" t="inlineStr">
+        <is>
+          <t>https://ctcleantrading.com.sg</t>
+        </is>
+      </c>
+      <c r="J393" s="2" t="inlineStr"/>
+      <c r="K393" s="2" t="inlineStr"/>
+      <c r="L393" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M393" s="2" t="inlineStr"/>
+      <c r="N393" s="2" t="inlineStr">
+        <is>
+          <t>ct.enquiry@ctcleantrading.com.sg</t>
+        </is>
+      </c>
+      <c r="O393" s="2" t="inlineStr"/>
+      <c r="P393" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q393" s="2" t="inlineStr">
+        <is>
+          <t>202000944N</t>
+        </is>
+      </c>
+      <c r="R393" s="2" t="inlineStr"/>
+      <c r="S393" s="2" t="inlineStr"/>
+      <c r="T393" s="2" t="inlineStr"/>
+      <c r="U393" s="2" t="inlineStr"/>
+      <c r="V393" s="2" t="inlineStr"/>
+      <c r="W393" s="2" t="inlineStr">
+        <is>
+          <t>Chris Toh</t>
+        </is>
+      </c>
+      <c r="X393" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y393" s="2" t="inlineStr"/>
+      <c r="Z393" s="2" t="inlineStr"/>
+      <c r="AA393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chris-toh-04926795/</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>Winecircle Pte Ltd</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>Winecircle Pte Ltd</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>122335</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>100 Peck Seah Street, Outram</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>079333</t>
+        </is>
+      </c>
+      <c r="I394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winecircle.sg</t>
+        </is>
+      </c>
+      <c r="J394" s="2" t="inlineStr"/>
+      <c r="K394" s="2" t="inlineStr"/>
+      <c r="L394" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M394" s="2" t="inlineStr"/>
+      <c r="N394" s="2" t="inlineStr">
+        <is>
+          <t>Friends@winecircle.sg</t>
+        </is>
+      </c>
+      <c r="O394" s="2" t="inlineStr"/>
+      <c r="P394" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q394" s="2" t="inlineStr">
+        <is>
+          <t>201915292C</t>
+        </is>
+      </c>
+      <c r="R394" s="2" t="inlineStr"/>
+      <c r="S394" s="2" t="inlineStr"/>
+      <c r="T394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winecirclesg</t>
+        </is>
+      </c>
+      <c r="U394" s="2" t="inlineStr"/>
+      <c r="V394" s="2" t="inlineStr"/>
+      <c r="W394" s="2" t="inlineStr">
+        <is>
+          <t>Jean-marie Lagier</t>
+        </is>
+      </c>
+      <c r="X394" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y394" s="2" t="inlineStr"/>
+      <c r="Z394" s="2" t="inlineStr"/>
+      <c r="AA394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jean-marie-lagier-4046374/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Singapore.xlsx
+++ b/BWI/bestwine_output/bestwine_Singapore.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA394"/>
+  <dimension ref="A1:AA397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -42743,6 +42743,289 @@
         </is>
       </c>
     </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>Blackbird Group Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>Blackbird Group Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>122332</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F395" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>International Plaza, 10 Anson Road, Downtown Core</t>
+        </is>
+      </c>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>079903</t>
+        </is>
+      </c>
+      <c r="I395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.blackbirdgroup.com.sg</t>
+        </is>
+      </c>
+      <c r="J395" s="2" t="inlineStr"/>
+      <c r="K395" s="2" t="inlineStr"/>
+      <c r="L395" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M395" s="2" t="inlineStr"/>
+      <c r="N395" s="2" t="inlineStr">
+        <is>
+          <t>info@blackbirdgroup.com.sg</t>
+        </is>
+      </c>
+      <c r="O395" s="2" t="inlineStr"/>
+      <c r="P395" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q395" s="2" t="inlineStr">
+        <is>
+          <t>201830342D</t>
+        </is>
+      </c>
+      <c r="R395" s="2" t="inlineStr"/>
+      <c r="S395" s="2" t="inlineStr"/>
+      <c r="T395" s="2" t="inlineStr"/>
+      <c r="U395" s="2" t="inlineStr"/>
+      <c r="V395" s="2" t="inlineStr"/>
+      <c r="W395" s="2" t="inlineStr">
+        <is>
+          <t>Richard Golds</t>
+        </is>
+      </c>
+      <c r="X395" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y395" s="2" t="inlineStr"/>
+      <c r="Z395" s="2" t="inlineStr"/>
+      <c r="AA395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/richard-golds-67b662a</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>Cities Trade Pte Ltd</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>Cities Trade Pte Ltd</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>122330</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>7 Mandai Link, Sungei Kadut</t>
+        </is>
+      </c>
+      <c r="H396" s="2" t="inlineStr">
+        <is>
+          <t>728653</t>
+        </is>
+      </c>
+      <c r="I396" s="2" t="inlineStr">
+        <is>
+          <t>https://ctcleantrading.com.sg</t>
+        </is>
+      </c>
+      <c r="J396" s="2" t="inlineStr"/>
+      <c r="K396" s="2" t="inlineStr"/>
+      <c r="L396" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M396" s="2" t="inlineStr"/>
+      <c r="N396" s="2" t="inlineStr">
+        <is>
+          <t>ct.enquiry@ctcleantrading.com.sg</t>
+        </is>
+      </c>
+      <c r="O396" s="2" t="inlineStr"/>
+      <c r="P396" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q396" s="2" t="inlineStr">
+        <is>
+          <t>202000944N</t>
+        </is>
+      </c>
+      <c r="R396" s="2" t="inlineStr"/>
+      <c r="S396" s="2" t="inlineStr"/>
+      <c r="T396" s="2" t="inlineStr"/>
+      <c r="U396" s="2" t="inlineStr"/>
+      <c r="V396" s="2" t="inlineStr"/>
+      <c r="W396" s="2" t="inlineStr">
+        <is>
+          <t>Chris Toh</t>
+        </is>
+      </c>
+      <c r="X396" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y396" s="2" t="inlineStr"/>
+      <c r="Z396" s="2" t="inlineStr"/>
+      <c r="AA396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chris-toh-04926795/</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>Winecircle Pte Ltd</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>Winecircle Pte Ltd</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>122335</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>100 Peck Seah Street, Outram</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>079333</t>
+        </is>
+      </c>
+      <c r="I397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winecircle.sg</t>
+        </is>
+      </c>
+      <c r="J397" s="2" t="inlineStr"/>
+      <c r="K397" s="2" t="inlineStr"/>
+      <c r="L397" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M397" s="2" t="inlineStr"/>
+      <c r="N397" s="2" t="inlineStr">
+        <is>
+          <t>Friends@winecircle.sg</t>
+        </is>
+      </c>
+      <c r="O397" s="2" t="inlineStr"/>
+      <c r="P397" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q397" s="2" t="inlineStr">
+        <is>
+          <t>201915292C</t>
+        </is>
+      </c>
+      <c r="R397" s="2" t="inlineStr"/>
+      <c r="S397" s="2" t="inlineStr"/>
+      <c r="T397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winecirclesg</t>
+        </is>
+      </c>
+      <c r="U397" s="2" t="inlineStr"/>
+      <c r="V397" s="2" t="inlineStr"/>
+      <c r="W397" s="2" t="inlineStr">
+        <is>
+          <t>Jean-marie Lagier</t>
+        </is>
+      </c>
+      <c r="X397" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y397" s="2" t="inlineStr"/>
+      <c r="Z397" s="2" t="inlineStr"/>
+      <c r="AA397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jean-marie-lagier-4046374/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Singapore.xlsx
+++ b/BWI/bestwine_output/bestwine_Singapore.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA397"/>
+  <dimension ref="A1:AA400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -43026,6 +43026,289 @@
         </is>
       </c>
     </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>Blackbird Group Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>Blackbird Group Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>122332</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>International Plaza, 10 Anson Road, Downtown Core</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>079903</t>
+        </is>
+      </c>
+      <c r="I398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.blackbirdgroup.com.sg</t>
+        </is>
+      </c>
+      <c r="J398" s="2" t="inlineStr"/>
+      <c r="K398" s="2" t="inlineStr"/>
+      <c r="L398" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M398" s="2" t="inlineStr"/>
+      <c r="N398" s="2" t="inlineStr">
+        <is>
+          <t>info@blackbirdgroup.com.sg</t>
+        </is>
+      </c>
+      <c r="O398" s="2" t="inlineStr"/>
+      <c r="P398" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q398" s="2" t="inlineStr">
+        <is>
+          <t>201830342D</t>
+        </is>
+      </c>
+      <c r="R398" s="2" t="inlineStr"/>
+      <c r="S398" s="2" t="inlineStr"/>
+      <c r="T398" s="2" t="inlineStr"/>
+      <c r="U398" s="2" t="inlineStr"/>
+      <c r="V398" s="2" t="inlineStr"/>
+      <c r="W398" s="2" t="inlineStr">
+        <is>
+          <t>Richard Golds</t>
+        </is>
+      </c>
+      <c r="X398" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y398" s="2" t="inlineStr"/>
+      <c r="Z398" s="2" t="inlineStr"/>
+      <c r="AA398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/richard-golds-67b662a</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>Cities Trade Pte Ltd</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>Cities Trade Pte Ltd</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>122330</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>7 Mandai Link, Sungei Kadut</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>728653</t>
+        </is>
+      </c>
+      <c r="I399" s="2" t="inlineStr">
+        <is>
+          <t>https://ctcleantrading.com.sg</t>
+        </is>
+      </c>
+      <c r="J399" s="2" t="inlineStr"/>
+      <c r="K399" s="2" t="inlineStr"/>
+      <c r="L399" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M399" s="2" t="inlineStr"/>
+      <c r="N399" s="2" t="inlineStr">
+        <is>
+          <t>ct.enquiry@ctcleantrading.com.sg</t>
+        </is>
+      </c>
+      <c r="O399" s="2" t="inlineStr"/>
+      <c r="P399" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q399" s="2" t="inlineStr">
+        <is>
+          <t>202000944N</t>
+        </is>
+      </c>
+      <c r="R399" s="2" t="inlineStr"/>
+      <c r="S399" s="2" t="inlineStr"/>
+      <c r="T399" s="2" t="inlineStr"/>
+      <c r="U399" s="2" t="inlineStr"/>
+      <c r="V399" s="2" t="inlineStr"/>
+      <c r="W399" s="2" t="inlineStr">
+        <is>
+          <t>Chris Toh</t>
+        </is>
+      </c>
+      <c r="X399" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y399" s="2" t="inlineStr"/>
+      <c r="Z399" s="2" t="inlineStr"/>
+      <c r="AA399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chris-toh-04926795/</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>Winecircle Pte Ltd</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>Winecircle Pte Ltd</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>122335</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>100 Peck Seah Street, Outram</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>079333</t>
+        </is>
+      </c>
+      <c r="I400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winecircle.sg</t>
+        </is>
+      </c>
+      <c r="J400" s="2" t="inlineStr"/>
+      <c r="K400" s="2" t="inlineStr"/>
+      <c r="L400" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M400" s="2" t="inlineStr"/>
+      <c r="N400" s="2" t="inlineStr">
+        <is>
+          <t>Friends@winecircle.sg</t>
+        </is>
+      </c>
+      <c r="O400" s="2" t="inlineStr"/>
+      <c r="P400" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q400" s="2" t="inlineStr">
+        <is>
+          <t>201915292C</t>
+        </is>
+      </c>
+      <c r="R400" s="2" t="inlineStr"/>
+      <c r="S400" s="2" t="inlineStr"/>
+      <c r="T400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winecirclesg</t>
+        </is>
+      </c>
+      <c r="U400" s="2" t="inlineStr"/>
+      <c r="V400" s="2" t="inlineStr"/>
+      <c r="W400" s="2" t="inlineStr">
+        <is>
+          <t>Jean-marie Lagier</t>
+        </is>
+      </c>
+      <c r="X400" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y400" s="2" t="inlineStr"/>
+      <c r="Z400" s="2" t="inlineStr"/>
+      <c r="AA400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jean-marie-lagier-4046374/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
